--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -10,8 +10,9 @@
   <sheets>
     <sheet name="ReadMe" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Parameters" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Planted_problems" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sources" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Price_bands" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Planted_problems" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="471">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -866,6 +867,159 @@
   </si>
   <si>
     <t xml:space="preserve">Customer and supplier names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 7 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset purchase cost as a multiple of its daily rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purchase_cost on asset. PLACEHOLDER: Kenyan prices not verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 7; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the fleet retired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets with status retired and a retired_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the fleet in repair at the as-of date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets with status in_repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread across categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products and assets are shared out evenly across their categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category on product and asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset purchase dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random dates from 2018-01-01 to 2026-03-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purchase_date on asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier brand word + model number + product type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prices and rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread evenly on a log scale between each category's low and high (sheet Price_bands). Product margins and asset purchase multiples sit around their central value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list_price, daily rate, standard_cost, purchase_cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACEHOLDERS for realistic scale. Not Kenyan market prices; I cannot verify those. Product bands sit inside parameter M08, asset bands inside M09.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low (KES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High (KES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microphones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 7; covered by the owner's 'use the proposed numbers' choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loudspeakers and amplifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixers and processors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Displays and projectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video conferencing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cables and connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lighting fixtures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control and automation devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset (daily rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conference audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sound reinforcement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projection and screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage lighting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED displays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video and streaming</t>
   </si>
   <si>
     <t xml:space="preserve">Planted problems (ground truth)</t>
@@ -1431,7 +1585,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1490,6 +1644,14 @@
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1850,7 +2012,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1859,7 +2021,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1914,7 +2076,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -4135,7 +4297,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
         <v>237</v>
       </c>
@@ -4173,7 +4335,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
         <v>243</v>
       </c>
@@ -4211,7 +4373,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
         <v>246</v>
       </c>
@@ -4249,7 +4411,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
         <v>248</v>
       </c>
@@ -4287,7 +4449,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
         <v>250</v>
       </c>
@@ -4325,7 +4487,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
         <v>252</v>
       </c>
@@ -4363,7 +4525,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
         <v>254</v>
       </c>
@@ -4401,7 +4563,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
         <v>257</v>
       </c>
@@ -4441,7 +4603,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
         <v>260</v>
       </c>
@@ -4481,7 +4643,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
         <v>262</v>
       </c>
@@ -4521,7 +4683,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
         <v>265</v>
       </c>
@@ -4559,7 +4721,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
         <v>269</v>
       </c>
@@ -4597,7 +4759,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
         <v>273</v>
       </c>
@@ -4635,7 +4797,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
         <v>277</v>
       </c>
@@ -4673,13 +4835,295 @@
         <v>242</v>
       </c>
     </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D74" s="8"/>
+      <c r="E74" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M74" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N74" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M56:M69" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M70:M76" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4699,6 +5143,393 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>900000</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F18" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4714,12 +5545,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>281</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>282</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4727,22 +5558,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>286</v>
+        <v>337</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -4750,15 +5581,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D5" s="15" t="n">
+        <v>342</v>
+      </c>
+      <c r="D5" s="17" t="n">
         <f aca="false">Parameters!E51</f>
         <v>12</v>
       </c>
@@ -4766,10 +5597,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -4777,15 +5608,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D6" s="15" t="n">
+        <v>347</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <f aca="false">Parameters!E52</f>
         <v>6</v>
       </c>
@@ -4793,10 +5624,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -4804,15 +5635,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D7" s="15" t="n">
+        <v>351</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <f aca="false">Parameters!E53</f>
         <v>6</v>
       </c>
@@ -4820,10 +5651,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>301</v>
+        <v>352</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -4831,15 +5662,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D8" s="15" t="n">
+        <v>342</v>
+      </c>
+      <c r="D8" s="17" t="n">
         <f aca="false">Parameters!E54</f>
         <v>8</v>
       </c>
@@ -4847,10 +5678,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>305</v>
+        <v>356</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -4858,15 +5689,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D9" s="15" t="n">
+        <v>347</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <f aca="false">Parameters!E55</f>
         <v>5</v>
       </c>
@@ -4874,10 +5705,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -4885,15 +5716,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>309</v>
+        <v>360</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D10" s="16" t="n">
+        <v>362</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <f aca="false">Parameters!E26</f>
         <v>0.25</v>
       </c>
@@ -4901,10 +5732,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -4912,15 +5743,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>314</v>
+        <v>365</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="D11" s="16" t="n">
+        <v>367</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">Parameters!E28</f>
         <v>-0.05</v>
       </c>
@@ -4928,10 +5759,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -4939,15 +5770,15 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>318</v>
+        <v>369</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="D12" s="15" t="n">
+        <v>371</v>
+      </c>
+      <c r="D12" s="17" t="n">
         <f aca="false">Parameters!E45</f>
         <v>4</v>
       </c>
@@ -4955,10 +5786,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -4966,15 +5797,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>323</v>
+        <v>374</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="D13" s="15" t="n">
+        <v>375</v>
+      </c>
+      <c r="D13" s="17" t="n">
         <f aca="false">Parameters!E38</f>
         <v>15</v>
       </c>
@@ -4982,10 +5813,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -4993,15 +5824,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="D14" s="16" t="n">
+        <v>378</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <f aca="false">Parameters!E34</f>
         <v>0.07</v>
       </c>
@@ -5009,10 +5840,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -5020,15 +5851,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>329</v>
+        <v>380</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="15" t="n">
+        <v>382</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <f aca="false">Parameters!E50</f>
         <v>10</v>
       </c>
@@ -5036,10 +5867,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -5047,15 +5878,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>334</v>
+        <v>385</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D16" s="17" t="n">
+        <v>386</v>
+      </c>
+      <c r="D16" s="19" t="n">
         <f aca="false">Parameters!E22</f>
         <v>15</v>
       </c>
@@ -5063,10 +5894,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>313</v>
+        <v>364</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -5083,7 +5914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5101,7 +5932,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>337</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5109,22 +5940,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>342</v>
+        <v>393</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>343</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5132,45 +5963,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>344</v>
+        <v>395</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>345</v>
+        <v>396</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>348</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>350</v>
+        <v>401</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>351</v>
+        <v>402</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>353</v>
+        <v>404</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5178,45 +6009,45 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>355</v>
+        <v>406</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>356</v>
+        <v>407</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>357</v>
+        <v>408</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>358</v>
+        <v>409</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>359</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>361</v>
+        <v>412</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5224,22 +6055,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>366</v>
+        <v>417</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>367</v>
+        <v>418</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>370</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5247,22 +6078,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>371</v>
+        <v>422</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>372</v>
+        <v>423</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>373</v>
+        <v>424</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5270,22 +6101,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>375</v>
+        <v>426</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>378</v>
+        <v>429</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>379</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5293,22 +6124,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>380</v>
+        <v>431</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5316,22 +6147,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>346</v>
+        <v>397</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>387</v>
+        <v>438</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5339,22 +6170,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>393</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5362,22 +6193,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>395</v>
+        <v>446</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>396</v>
+        <v>447</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>398</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5385,45 +6216,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>401</v>
+        <v>452</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>403</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>405</v>
+        <v>456</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>406</v>
+        <v>457</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>407</v>
+        <v>458</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>408</v>
+        <v>459</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>409</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5431,45 +6262,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>410</v>
+        <v>461</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>411</v>
+        <v>462</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>412</v>
+        <v>463</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>414</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>417</v>
+        <v>468</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>418</v>
+        <v>469</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>419</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="529">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -953,6 +953,183 @@
     <t xml:space="preserve">list_price, daily rate, standard_cost, purchase_cost</t>
   </si>
   <si>
+    <t xml:space="preserve">C06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 8 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of non-won quotes that expire with no answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quotes with status expired and no decision date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 8; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of quotes and jobs handled by the Nairobi office (rest: Mombasa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office_name on quotes, jobs, orders and bookings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a duplicated customer's records that use the duplicate code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makes the duplicate customers matter: some quotes and jobs point to the duplicate code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost noise on equipment, subcontractor and transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual cost against quoted cost, ordinary jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a job's quoted cost: Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The five shares CM1 to CM5 must add up to 100%. Labour (CM2 + CM3) is 46% of cost, about 30% of price at a 35% margin, matching M02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a job's quoted cost: Installation labour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a job's quoted cost: Programming and commissioning labour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As above. Commissioning is where estimates go wrong most (S1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a job's quoted cost: Subcontractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CM5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of a job's quoted cost: Transport and logistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation labour rate (KES per hour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit_cost on installation labour lines. PLACEHOLDER: Kenyan rates not verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programming and commissioning labour rate (KES per hour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit_cost on commissioning labour lines. PLACEHOLDER: Kenyan rates not verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commissioning-heavy job types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control room installation; Smart office and automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These get the labour overrun M04 on commissioning labour (planted problem X06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss-making job type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditorium and hall fit-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average margin set by M06 (planted problem X07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job value scale factor by job type (multiplies the M07 spread)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maintenance 0.3; Public address 0.5; Conference room 0.6; Stage lighting 0.8; Video wall 1.0; Smart office 1.0; Control room 2.0; Auditorium 2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">So a maintenance contract is not as big as an auditorium fit-out. Values are clipped to the M07 range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quote dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread evenly from 2023-10-01 to 2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quote_date. Quotes decided after the as-of date stay open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts 0 to 30 days after the decision; lasts about 7 to 72 days, longer for bigger jobs; no cancelled jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">start_date and end_date. Jobs not finished by the as-of date are in_progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How the quote decision time is spread (shape)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days from quote to decision = low + (high - low) x (random number to the power 4). The mean matches the C04 central value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most quotes are decided quickly, a few take long</t>
+  </si>
+  <si>
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
   </si>
   <si>
@@ -1257,9 +1434,6 @@
   </si>
   <si>
     <t xml:space="preserve">Customers of one software product; 'margin' not defined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S4</t>
   </si>
   <si>
     <t xml:space="preserve">CEPro: 43 metrics for the A/V industry (2018)</t>
@@ -1585,7 +1759,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1644,14 +1818,6 @@
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2012,7 +2178,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2021,7 +2187,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2076,7 +2242,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -4835,7 +5001,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
         <v>281</v>
       </c>
@@ -4877,7 +5043,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
         <v>287</v>
       </c>
@@ -4919,7 +5085,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
         <v>290</v>
       </c>
@@ -4961,7 +5127,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
         <v>293</v>
       </c>
@@ -4999,7 +5165,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
         <v>297</v>
       </c>
@@ -5037,7 +5203,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
         <v>301</v>
       </c>
@@ -5075,7 +5241,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
         <v>305</v>
       </c>
@@ -5113,8 +5279,688 @@
         <v>286</v>
       </c>
     </row>
+    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D77" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K77" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N77" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D78" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M78" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N78" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="L80" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M80" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N80" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J81" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K81" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M82" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N82" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="D83" s="8"/>
+      <c r="E83" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J83" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K83" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L84" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="13" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="L86" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M86" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N86" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K88" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L88" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M88" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N88" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M92" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N92" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
@@ -5124,6 +5970,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M70:M76" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M77:M93" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5146,35 +5996,35 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>314</v>
+        <v>373</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -5186,12 +6036,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -5206,15 +6056,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -5229,15 +6079,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>319</v>
+        <v>378</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -5252,15 +6102,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -5275,15 +6125,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -5298,15 +6148,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -5321,15 +6171,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -5344,15 +6194,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -5367,15 +6217,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>326</v>
+        <v>385</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -5390,15 +6240,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -5413,15 +6263,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -5436,15 +6286,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>329</v>
+        <v>388</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -5459,15 +6309,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -5482,15 +6332,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>325</v>
+        <v>384</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -5505,7 +6355,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>317</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5545,12 +6395,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>332</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5558,22 +6408,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>339</v>
+        <v>398</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -5581,15 +6431,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>340</v>
+        <v>399</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="D5" s="17" t="n">
+        <v>401</v>
+      </c>
+      <c r="D5" s="15" t="n">
         <f aca="false">Parameters!E51</f>
         <v>12</v>
       </c>
@@ -5597,10 +6447,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -5608,15 +6458,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>345</v>
+        <v>404</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>346</v>
+        <v>405</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="17" t="n">
+        <v>406</v>
+      </c>
+      <c r="D6" s="15" t="n">
         <f aca="false">Parameters!E52</f>
         <v>6</v>
       </c>
@@ -5624,10 +6474,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -5635,15 +6485,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D7" s="17" t="n">
+        <v>410</v>
+      </c>
+      <c r="D7" s="15" t="n">
         <f aca="false">Parameters!E53</f>
         <v>6</v>
       </c>
@@ -5651,10 +6501,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -5662,15 +6512,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="D8" s="17" t="n">
+        <v>401</v>
+      </c>
+      <c r="D8" s="15" t="n">
         <f aca="false">Parameters!E54</f>
         <v>8</v>
       </c>
@@ -5678,10 +6528,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -5689,15 +6539,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>358</v>
+        <v>417</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D9" s="17" t="n">
+        <v>406</v>
+      </c>
+      <c r="D9" s="15" t="n">
         <f aca="false">Parameters!E55</f>
         <v>5</v>
       </c>
@@ -5705,10 +6555,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>359</v>
+        <v>418</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -5716,15 +6566,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>360</v>
+        <v>419</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>361</v>
+        <v>420</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D10" s="18" t="n">
+        <v>421</v>
+      </c>
+      <c r="D10" s="16" t="n">
         <f aca="false">Parameters!E26</f>
         <v>0.25</v>
       </c>
@@ -5732,10 +6582,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>363</v>
+        <v>422</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -5743,15 +6593,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="D11" s="18" t="n">
+        <v>426</v>
+      </c>
+      <c r="D11" s="16" t="n">
         <f aca="false">Parameters!E28</f>
         <v>-0.05</v>
       </c>
@@ -5759,10 +6609,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -5770,15 +6620,15 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>370</v>
+        <v>429</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="D12" s="17" t="n">
+        <v>430</v>
+      </c>
+      <c r="D12" s="15" t="n">
         <f aca="false">Parameters!E45</f>
         <v>4</v>
       </c>
@@ -5786,10 +6636,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>372</v>
+        <v>431</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -5797,15 +6647,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>374</v>
+        <v>433</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="D13" s="17" t="n">
+        <v>434</v>
+      </c>
+      <c r="D13" s="15" t="n">
         <f aca="false">Parameters!E38</f>
         <v>15</v>
       </c>
@@ -5813,10 +6663,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -5824,15 +6674,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>377</v>
+        <v>436</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="D14" s="18" t="n">
+        <v>437</v>
+      </c>
+      <c r="D14" s="16" t="n">
         <f aca="false">Parameters!E34</f>
         <v>0.07</v>
       </c>
@@ -5840,10 +6690,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>379</v>
+        <v>438</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -5851,15 +6701,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>381</v>
+        <v>440</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D15" s="17" t="n">
+        <v>441</v>
+      </c>
+      <c r="D15" s="15" t="n">
         <f aca="false">Parameters!E50</f>
         <v>10</v>
       </c>
@@ -5867,10 +6717,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>383</v>
+        <v>442</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -5878,15 +6728,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="D16" s="19" t="n">
+        <v>445</v>
+      </c>
+      <c r="D16" s="17" t="n">
         <f aca="false">Parameters!E22</f>
         <v>15</v>
       </c>
@@ -5894,10 +6744,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>387</v>
+        <v>446</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>364</v>
+        <v>423</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -5932,7 +6782,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>388</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5940,22 +6790,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>389</v>
+        <v>448</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>390</v>
+        <v>449</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>394</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5963,45 +6813,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>395</v>
+        <v>454</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>396</v>
+        <v>455</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>398</v>
+        <v>457</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>399</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>400</v>
+        <v>459</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>402</v>
+        <v>461</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>404</v>
+        <v>463</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>405</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6009,45 +6859,45 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>406</v>
+        <v>465</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>407</v>
+        <v>466</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>408</v>
+        <v>467</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>409</v>
+        <v>468</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>410</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>411</v>
+        <v>326</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>412</v>
+        <v>470</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>413</v>
+        <v>471</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>415</v>
+        <v>473</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>416</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6055,22 +6905,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>417</v>
+        <v>475</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>418</v>
+        <v>476</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>419</v>
+        <v>477</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>421</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6078,22 +6928,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>422</v>
+        <v>480</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6101,22 +6951,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>426</v>
+        <v>484</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>429</v>
+        <v>487</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6124,22 +6974,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>434</v>
+        <v>492</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>435</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6147,22 +6997,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>436</v>
+        <v>494</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>437</v>
+        <v>495</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>397</v>
+        <v>456</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>438</v>
+        <v>496</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>439</v>
+        <v>497</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6170,22 +7020,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>440</v>
+        <v>498</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>441</v>
+        <v>499</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>442</v>
+        <v>500</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>443</v>
+        <v>501</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>444</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6193,22 +7043,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>445</v>
+        <v>503</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>447</v>
+        <v>505</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6216,45 +7066,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>451</v>
+        <v>509</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>452</v>
+        <v>510</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>453</v>
+        <v>511</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>454</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>455</v>
+        <v>513</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>456</v>
+        <v>514</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>457</v>
+        <v>515</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>458</v>
+        <v>516</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>459</v>
+        <v>517</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>460</v>
+        <v>518</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6262,45 +7112,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>461</v>
+        <v>519</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>462</v>
+        <v>520</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>463</v>
+        <v>521</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>464</v>
+        <v>522</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>465</v>
+        <v>523</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>466</v>
+        <v>524</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>467</v>
+        <v>525</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>468</v>
+        <v>526</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>433</v>
+        <v>491</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>469</v>
+        <v>527</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>470</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="563">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -1128,6 +1128,108 @@
   </si>
   <si>
     <t xml:space="preserve">Most quotes are decided quickly, a few take long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 9 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product sales orders over the window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows in sales_order. Includes orders that come from quotes and orders with no quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 9; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of sales orders that come from a quote (the rest are counter or walk-in sales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets how many products quotes are created: orders from quotes divided by the win rate C02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock adjustments over the window (count, damage or count differences)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock_movement rows of type adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount given on product sales (share off list price)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unit_price = list price x (1 - discount). Most discounts are small, a few are large (the draw is squared)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock bought each quarter as a multiple of that quarter's sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase quantity = quarter's sales x this + 5 units. Keeps stock from running out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock buying pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One purchase per product per quarter (a few days before the quarter starts), plus 5 spare units. Dead-stock products also get one big extra purchase between 2025-04-01 and 2025-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock_movement purchases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead-stock rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead-stock products have no sales orders after 2025-09-27 (12 months before the as-of date, with a few days of room for delivery)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planted problem X11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largest quantity per order line, by category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cables 40; Lighting 12; Control 10; Microphones 8; Loudspeakers 8; Displays 6; Video conferencing 4; Mixers 3. Most lines are small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quantity on sales_order_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales order timing and size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 to 4 product lines per order. Stock leaves 0 to 2 days after the order date. Orders in the last 7 days are still open. No cancelled orders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales_order and stock_movement dates</t>
   </si>
   <si>
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
@@ -1617,12 +1719,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0%;\-0%"/>
     <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -1759,7 +1862,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1817,6 +1920,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2178,7 +2285,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2187,7 +2294,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2242,7 +2349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -5279,7 +5386,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
         <v>309</v>
       </c>
@@ -5321,7 +5428,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
         <v>315</v>
       </c>
@@ -5363,7 +5470,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
         <v>318</v>
       </c>
@@ -5405,7 +5512,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
         <v>321</v>
       </c>
@@ -5447,7 +5554,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
         <v>324</v>
       </c>
@@ -5487,7 +5594,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
         <v>328</v>
       </c>
@@ -5527,7 +5634,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
         <v>331</v>
       </c>
@@ -5567,7 +5674,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
         <v>334</v>
       </c>
@@ -5605,7 +5712,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
         <v>336</v>
       </c>
@@ -5643,7 +5750,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
         <v>338</v>
       </c>
@@ -5685,7 +5792,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
         <v>341</v>
       </c>
@@ -5727,7 +5834,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
         <v>344</v>
       </c>
@@ -5767,7 +5874,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
         <v>348</v>
       </c>
@@ -5805,7 +5912,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
         <v>352</v>
       </c>
@@ -5843,7 +5950,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
         <v>356</v>
       </c>
@@ -5881,7 +5988,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
         <v>360</v>
       </c>
@@ -5919,7 +6026,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
         <v>364</v>
       </c>
@@ -5959,8 +6066,370 @@
         <v>314</v>
       </c>
     </row>
+    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K94" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="L94" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N94" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K96" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M96" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N96" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M97" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N97" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D98" s="15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M98" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N98" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M99" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N99" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K100" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M100" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N100" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K101" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="D102" s="8"/>
+      <c r="E102" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="M102" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N102" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
@@ -5974,6 +6443,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M77:M93" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M94:M102" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6005,26 +6478,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>373</v>
+        <v>407</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -6038,10 +6511,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -6056,15 +6529,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -6079,15 +6552,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -6102,15 +6575,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>379</v>
+        <v>413</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -6125,15 +6598,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -6148,15 +6621,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -6171,15 +6644,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -6194,15 +6667,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -6217,15 +6690,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -6240,15 +6713,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -6263,15 +6736,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -6286,15 +6759,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -6309,15 +6782,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -6332,15 +6805,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -6355,7 +6828,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>376</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -6395,12 +6868,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6408,22 +6881,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>396</v>
+        <v>430</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>397</v>
+        <v>431</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -6431,15 +6904,15 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>399</v>
+        <v>433</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>400</v>
+        <v>434</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="D5" s="15" t="n">
+        <v>435</v>
+      </c>
+      <c r="D5" s="16" t="n">
         <f aca="false">Parameters!E51</f>
         <v>12</v>
       </c>
@@ -6447,10 +6920,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -6458,15 +6931,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="D6" s="15" t="n">
+        <v>440</v>
+      </c>
+      <c r="D6" s="16" t="n">
         <f aca="false">Parameters!E52</f>
         <v>6</v>
       </c>
@@ -6474,10 +6947,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -6485,15 +6958,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="D7" s="15" t="n">
+        <v>444</v>
+      </c>
+      <c r="D7" s="16" t="n">
         <f aca="false">Parameters!E53</f>
         <v>6</v>
       </c>
@@ -6501,10 +6974,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -6512,15 +6985,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>414</v>
+        <v>448</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="D8" s="15" t="n">
+        <v>435</v>
+      </c>
+      <c r="D8" s="16" t="n">
         <f aca="false">Parameters!E54</f>
         <v>8</v>
       </c>
@@ -6528,10 +7001,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -6539,15 +7012,15 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>416</v>
+        <v>450</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>417</v>
+        <v>451</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="D9" s="15" t="n">
+        <v>440</v>
+      </c>
+      <c r="D9" s="16" t="n">
         <f aca="false">Parameters!E55</f>
         <v>5</v>
       </c>
@@ -6555,10 +7028,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>403</v>
+        <v>437</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -6566,15 +7039,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="D10" s="16" t="n">
+        <v>455</v>
+      </c>
+      <c r="D10" s="17" t="n">
         <f aca="false">Parameters!E26</f>
         <v>0.25</v>
       </c>
@@ -6582,10 +7055,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -6593,15 +7066,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="D11" s="16" t="n">
+        <v>460</v>
+      </c>
+      <c r="D11" s="17" t="n">
         <f aca="false">Parameters!E28</f>
         <v>-0.05</v>
       </c>
@@ -6609,10 +7082,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>427</v>
+        <v>461</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -6620,15 +7093,15 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>429</v>
+        <v>463</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="D12" s="15" t="n">
+        <v>464</v>
+      </c>
+      <c r="D12" s="16" t="n">
         <f aca="false">Parameters!E45</f>
         <v>4</v>
       </c>
@@ -6636,10 +7109,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>431</v>
+        <v>465</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -6647,15 +7120,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>432</v>
+        <v>466</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>433</v>
+        <v>467</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="D13" s="15" t="n">
+        <v>468</v>
+      </c>
+      <c r="D13" s="16" t="n">
         <f aca="false">Parameters!E38</f>
         <v>15</v>
       </c>
@@ -6663,10 +7136,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -6674,15 +7147,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>436</v>
+        <v>470</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="D14" s="16" t="n">
+        <v>471</v>
+      </c>
+      <c r="D14" s="17" t="n">
         <f aca="false">Parameters!E34</f>
         <v>0.07</v>
       </c>
@@ -6690,10 +7163,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -6701,15 +7174,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="D15" s="15" t="n">
+        <v>475</v>
+      </c>
+      <c r="D15" s="16" t="n">
         <f aca="false">Parameters!E50</f>
         <v>10</v>
       </c>
@@ -6717,10 +7190,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -6728,15 +7201,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>443</v>
+        <v>477</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>444</v>
+        <v>478</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="D16" s="17" t="n">
+        <v>479</v>
+      </c>
+      <c r="D16" s="18" t="n">
         <f aca="false">Parameters!E22</f>
         <v>15</v>
       </c>
@@ -6744,10 +7217,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>446</v>
+        <v>480</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>423</v>
+        <v>457</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -6782,7 +7255,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>447</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6790,22 +7263,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>449</v>
+        <v>483</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>452</v>
+        <v>486</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>453</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6813,45 +7286,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>460</v>
+        <v>494</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>461</v>
+        <v>495</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>463</v>
+        <v>497</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6859,22 +7332,22 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6882,22 +7355,22 @@
         <v>326</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>470</v>
+        <v>504</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6905,22 +7378,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6928,22 +7401,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6951,22 +7424,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>484</v>
+        <v>518</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>485</v>
+        <v>519</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>488</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6974,22 +7447,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>489</v>
+        <v>523</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>493</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6997,22 +7470,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>494</v>
+        <v>528</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>495</v>
+        <v>529</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>496</v>
+        <v>530</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7020,22 +7493,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>502</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7043,22 +7516,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>506</v>
+        <v>540</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>507</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7066,45 +7539,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>513</v>
+        <v>547</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>515</v>
+        <v>549</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>516</v>
+        <v>550</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>518</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7112,45 +7585,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>519</v>
+        <v>553</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>521</v>
+        <v>555</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>522</v>
+        <v>556</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>523</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>524</v>
+        <v>558</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>525</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>491</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>527</v>
+        <v>561</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>528</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="599">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -1230,6 +1230,114 @@
   </si>
   <si>
     <t xml:space="preserve">sales_order and stock_movement dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 10 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANTED: utilisation of the idle assets (share of available days on hire)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assets marked idle in Stage 7. Must stay under 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 10; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANTED: repair-prone assets have damage this many times more often</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplies the time lost to repairs (R04) for the idle, repair-prone assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANTED: repair-prone assets cost this many times more per repair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplies the repair cost (R05) for the idle, repair-prone assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discount on rental rates (share off the rate card)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One discount per booking. Most are small, a few large (the draw is squared)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How rentals are built</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each asset gets its own non-overlapping run of rentals, sized to hit its utilisation target. Rentals of different assets that start on the same day and last the same time are grouped into one booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gives exact utilisation without double-bookings (except the planted ones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental length in days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (20%), 2 (25%), 3 (20%), 4 (12%), 5 (10%), 7 (8%), 10 (5%). Mean 3.34 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rental_booking start_date and end_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisation target per asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A random value inside the register range for its group: event kit R01, core fleet R02, idle assets I01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7, S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group averages therefore sit at the central values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage is found when a rental ends, and the asset is then out of service for 2 to 10 days. One routine service a year (no downtime). Assets marked in_repair have a 30-day repair running at the as-of date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maintenance_event rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is not modelled in rentals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No seasonality (R06 is not used), no cancelled or future bookings, no deposits. Every booking is completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known limitations</t>
   </si>
   <si>
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
@@ -2285,7 +2393,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2294,7 +2402,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2349,7 +2457,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6066,7 +6174,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
         <v>368</v>
       </c>
@@ -6108,7 +6216,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
         <v>374</v>
       </c>
@@ -6150,7 +6258,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
         <v>377</v>
       </c>
@@ -6192,7 +6300,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
         <v>380</v>
       </c>
@@ -6234,7 +6342,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
         <v>383</v>
       </c>
@@ -6276,7 +6384,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
         <v>386</v>
       </c>
@@ -6314,7 +6422,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
         <v>390</v>
       </c>
@@ -6352,7 +6460,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
         <v>394</v>
       </c>
@@ -6390,7 +6498,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
         <v>398</v>
       </c>
@@ -6428,8 +6536,370 @@
         <v>373</v>
       </c>
     </row>
+    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K103" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M103" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N103" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K104" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M104" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N104" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K105" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M105" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N105" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="D106" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K106" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M106" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N106" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="D107" s="8"/>
+      <c r="E107" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="F107" s="8"/>
+      <c r="G107" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M107" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N107" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="D108" s="8"/>
+      <c r="E108" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F108" s="8"/>
+      <c r="G108" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K108" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M108" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N108" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="D109" s="8"/>
+      <c r="E109" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F109" s="8"/>
+      <c r="G109" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J109" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K109" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M109" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D110" s="8"/>
+      <c r="E110" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J110" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K110" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M110" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N110" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D111" s="8"/>
+      <c r="E111" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="M111" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N111" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
@@ -6447,6 +6917,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M94:M102" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M103:M111" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6478,26 +6952,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>402</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>403</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -6511,10 +6985,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -6529,15 +7003,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -6552,15 +7026,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -6575,15 +7049,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -6598,15 +7072,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -6621,15 +7095,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -6644,15 +7118,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -6667,15 +7141,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -6690,15 +7164,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>419</v>
+        <v>455</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -6713,15 +7187,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -6736,15 +7210,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -6759,15 +7233,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>422</v>
+        <v>458</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -6782,15 +7256,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -6805,15 +7279,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>418</v>
+        <v>454</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -6828,7 +7302,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>410</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -6868,12 +7342,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>425</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>426</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6881,22 +7355,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>432</v>
+        <v>468</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -6904,13 +7378,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">Parameters!E51</f>
@@ -6920,10 +7394,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -6931,13 +7405,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">Parameters!E52</f>
@@ -6947,10 +7421,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -6958,13 +7432,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">Parameters!E53</f>
@@ -6974,10 +7448,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>445</v>
+        <v>481</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -6985,13 +7459,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>448</v>
+        <v>484</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">Parameters!E54</f>
@@ -7001,10 +7475,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>449</v>
+        <v>485</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -7012,13 +7486,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>451</v>
+        <v>487</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>440</v>
+        <v>476</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">Parameters!E55</f>
@@ -7028,10 +7502,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -7039,13 +7513,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>454</v>
+        <v>490</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>455</v>
+        <v>491</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">Parameters!E26</f>
@@ -7055,10 +7529,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>456</v>
+        <v>492</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -7066,13 +7540,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>460</v>
+        <v>496</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Parameters!E28</f>
@@ -7082,10 +7556,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>461</v>
+        <v>497</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -7093,13 +7567,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>463</v>
+        <v>499</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">Parameters!E45</f>
@@ -7109,10 +7583,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>465</v>
+        <v>501</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -7120,13 +7594,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>467</v>
+        <v>503</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">Parameters!E38</f>
@@ -7136,10 +7610,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -7147,13 +7621,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>470</v>
+        <v>506</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Parameters!E34</f>
@@ -7163,10 +7637,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -7174,13 +7648,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>473</v>
+        <v>509</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>474</v>
+        <v>510</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">Parameters!E50</f>
@@ -7190,10 +7664,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>476</v>
+        <v>512</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -7201,13 +7675,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>477</v>
+        <v>513</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>478</v>
+        <v>514</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">Parameters!E22</f>
@@ -7217,10 +7691,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -7255,7 +7729,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>481</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7263,22 +7737,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>482</v>
+        <v>518</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>484</v>
+        <v>520</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>486</v>
+        <v>522</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7286,45 +7760,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>489</v>
+        <v>525</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>495</v>
+        <v>531</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7332,22 +7806,22 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>500</v>
+        <v>536</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7355,22 +7829,22 @@
         <v>326</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>505</v>
+        <v>541</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>506</v>
+        <v>542</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7378,22 +7852,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>509</v>
+        <v>545</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>510</v>
+        <v>546</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7401,22 +7875,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>516</v>
+        <v>552</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>517</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7424,22 +7898,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>521</v>
+        <v>557</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>522</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7447,22 +7921,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>523</v>
+        <v>559</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>525</v>
+        <v>561</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>527</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7470,22 +7944,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>528</v>
+        <v>564</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>529</v>
+        <v>565</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>531</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7493,22 +7967,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>533</v>
+        <v>569</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>534</v>
+        <v>570</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>536</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7516,22 +7990,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>539</v>
+        <v>575</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>540</v>
+        <v>576</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>541</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7539,45 +8013,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>542</v>
+        <v>578</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>543</v>
+        <v>579</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>544</v>
+        <v>580</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>545</v>
+        <v>581</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>547</v>
+        <v>583</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>548</v>
+        <v>584</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>551</v>
+        <v>587</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>552</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7585,45 +8059,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>553</v>
+        <v>589</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>554</v>
+        <v>590</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>555</v>
+        <v>591</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>556</v>
+        <v>592</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>557</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>558</v>
+        <v>594</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>559</v>
+        <v>595</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>560</v>
+        <v>596</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>525</v>
+        <v>561</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>561</v>
+        <v>597</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>562</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="616">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -1338,6 +1338,57 @@
   </si>
   <si>
     <t xml:space="preserve">Known limitations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 11 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of rental bookings that had a formal quote (the rest are repeat or simple bookings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets how many rental quotes are won. Rental quotes in total = won quotes divided by the win rate C03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 11; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct cost of a rental as a share of its price (crew, handling, transport; shown on the quote only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quoted_cost on rental quotes. Rental costs are not recorded anywhere else in the model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price of rental quotes that were not won</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Between 1 and 6 randomly chosen assets, for a rental length drawn as in G33, at their rate-card prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quoted_price on lost, expired and open rental quotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timing of won rental quotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The quote is decided (days drawn as in G27), then the rental starts 1 to 14 days later. Bookings in the first weeks of history cannot have a quote and are left without one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quote_date and decision_date on won rental quotes</t>
   </si>
   <si>
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
@@ -2393,7 +2444,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2402,7 +2453,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2457,7 +2508,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6536,7 +6587,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="s">
         <v>402</v>
       </c>
@@ -6578,7 +6629,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="s">
         <v>408</v>
       </c>
@@ -6620,7 +6671,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="s">
         <v>411</v>
       </c>
@@ -6662,7 +6713,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="s">
         <v>414</v>
       </c>
@@ -6704,7 +6755,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
         <v>417</v>
       </c>
@@ -6742,7 +6793,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
         <v>421</v>
       </c>
@@ -6780,7 +6831,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="s">
         <v>425</v>
       </c>
@@ -6820,7 +6871,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="s">
         <v>430</v>
       </c>
@@ -6860,7 +6911,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="s">
         <v>434</v>
       </c>
@@ -6898,8 +6949,170 @@
         <v>407</v>
       </c>
     </row>
+    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="D112" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E112" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M112" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N112" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K113" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M113" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N113" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D114" s="8"/>
+      <c r="E114" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="F114" s="8"/>
+      <c r="G114" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K114" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M114" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N114" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D115" s="8"/>
+      <c r="E115" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M115" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N115" s="10" t="s">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
@@ -6921,6 +7134,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M103:M111" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M112:M115" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6952,26 +7169,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -6985,10 +7202,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -7003,15 +7220,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -7026,15 +7243,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -7049,15 +7266,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -7072,15 +7289,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -7095,15 +7312,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -7118,15 +7335,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -7141,15 +7358,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -7164,15 +7381,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -7187,15 +7404,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -7210,15 +7427,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -7233,15 +7450,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -7256,15 +7473,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -7279,15 +7496,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -7302,7 +7519,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -7342,12 +7559,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7355,22 +7572,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -7378,13 +7595,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">Parameters!E51</f>
@@ -7394,10 +7611,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -7405,13 +7622,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">Parameters!E52</f>
@@ -7421,10 +7638,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -7432,13 +7649,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">Parameters!E53</f>
@@ -7448,10 +7665,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -7459,13 +7676,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">Parameters!E54</f>
@@ -7475,10 +7692,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -7486,13 +7703,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">Parameters!E55</f>
@@ -7502,10 +7719,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -7513,13 +7730,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">Parameters!E26</f>
@@ -7529,10 +7746,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -7540,13 +7757,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Parameters!E28</f>
@@ -7556,10 +7773,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -7567,13 +7784,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">Parameters!E45</f>
@@ -7583,10 +7800,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -7594,13 +7811,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">Parameters!E38</f>
@@ -7610,10 +7827,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -7621,13 +7838,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Parameters!E34</f>
@@ -7637,10 +7854,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -7648,13 +7865,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">Parameters!E50</f>
@@ -7664,10 +7881,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -7675,13 +7892,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">Parameters!E22</f>
@@ -7691,10 +7908,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -7729,7 +7946,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7737,22 +7954,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7760,45 +7977,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>528</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>529</v>
+        <v>546</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7806,22 +8023,22 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>538</v>
+        <v>555</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>539</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7829,22 +8046,22 @@
         <v>326</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7852,22 +8069,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7875,22 +8092,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7898,22 +8115,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7921,22 +8138,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7944,22 +8161,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7967,22 +8184,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7990,22 +8207,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8013,45 +8230,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8059,45 +8276,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="639">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -1389,6 +1389,75 @@
   </si>
   <si>
     <t xml:space="preserve">quote_date and decision_date on won rental quotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 12 additions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of the business (by customer activity) that comes from customers who pay promptly, within 30 days of the invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets which customers are prompt payers, so that the share of invoices paid over 30 days after the invoice (P06) lands near 60%. Prompt payers are never the habitual late payers (P07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCEPTED (added Stage 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 12; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How invoices are raised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projects: 1 to 4 invoices per job (a deposit at the start, the last at the end); only invoices dated up to the as-of date exist. Products: one invoice per delivered order, 0 to 2 days after the order. Rentals: one invoice per booking, 0 to 3 days after it ends. VAT is added at the P11 rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice dates and amounts. The VAT rate still needs verifying (row P11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How fast each kind of customer pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitual late payers (P07): the payment terms + 60 to 120 days. Prompt payers (P12): 5 to 30 days after the invoice. Everyone else: the sector ranges P02 to P05, with the average at the central value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10, S11, S12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment dates. Customers keep their payment habit for all their invoices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parts and bundles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some invoices are paid in two parts (P08; second part 10 to 40 days later). Some invoices of the same customer paid in the same week are paid by one payment (P09). A payment is only recorded if it falls on or before the as-of date, so late invoices stay unpaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment and payment_allocation rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment method mix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank transfer 55%, mobile money 25%, cheque 15%, cash 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_method</t>
   </si>
   <si>
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
@@ -2444,7 +2513,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">COUNTA(Parameters!A5:A200)</f>
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2453,7 +2522,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2508,7 +2577,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6949,7 +7018,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="s">
         <v>438</v>
       </c>
@@ -6991,7 +7060,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="s">
         <v>444</v>
       </c>
@@ -7033,7 +7102,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="s">
         <v>447</v>
       </c>
@@ -7071,7 +7140,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="s">
         <v>451</v>
       </c>
@@ -7111,8 +7180,208 @@
         <v>443</v>
       </c>
     </row>
+    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="D116" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E116" s="13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="J116" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K116" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M116" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N116" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D117" s="8"/>
+      <c r="E117" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J117" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="K117" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M117" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N117" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D118" s="8"/>
+      <c r="E118" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M118" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N118" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D119" s="8"/>
+      <c r="E119" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="F119" s="8"/>
+      <c r="G119" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K119" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M119" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="D120" s="8"/>
+      <c r="E120" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M120" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N120" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M55" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
@@ -7138,6 +7407,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M112:M115" type="list">
+      <formula1>"Accept,Change,Reject"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M116:M120" type="list">
       <formula1>"Accept,Change,Reject"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7169,26 +7442,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -7202,10 +7475,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -7220,15 +7493,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -7243,15 +7516,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -7266,15 +7539,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -7289,15 +7562,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -7312,15 +7585,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -7335,15 +7608,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -7358,15 +7631,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -7381,15 +7654,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -7404,15 +7677,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -7427,15 +7700,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -7450,15 +7723,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -7473,15 +7746,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -7496,15 +7769,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -7519,7 +7792,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -7559,12 +7832,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7572,22 +7845,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -7595,13 +7868,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">Parameters!E51</f>
@@ -7611,10 +7884,10 @@
         <v>221</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -7622,13 +7895,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">Parameters!E52</f>
@@ -7638,10 +7911,10 @@
         <v>225</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -7649,13 +7922,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">Parameters!E53</f>
@@ -7665,10 +7938,10 @@
         <v>228</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -7676,13 +7949,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>500</v>
+        <v>523</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">Parameters!E54</f>
@@ -7692,10 +7965,10 @@
         <v>231</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -7703,13 +7976,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">Parameters!E55</f>
@@ -7719,10 +7992,10 @@
         <v>234</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -7730,13 +8003,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">Parameters!E26</f>
@@ -7746,10 +8019,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>509</v>
+        <v>532</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -7757,13 +8030,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>511</v>
+        <v>534</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>512</v>
+        <v>535</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>513</v>
+        <v>536</v>
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">Parameters!E28</f>
@@ -7773,10 +8046,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -7784,13 +8057,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">Parameters!E45</f>
@@ -7800,10 +8073,10 @@
         <v>197</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -7811,13 +8084,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>521</v>
+        <v>544</v>
       </c>
       <c r="D13" s="16" t="n">
         <f aca="false">Parameters!E38</f>
@@ -7827,10 +8100,10 @@
         <v>171</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -7838,13 +8111,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">Parameters!E34</f>
@@ -7854,10 +8127,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -7865,13 +8138,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
       <c r="D15" s="16" t="n">
         <f aca="false">Parameters!E50</f>
@@ -7881,10 +8154,10 @@
         <v>217</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -7892,13 +8165,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">Parameters!E22</f>
@@ -7908,10 +8181,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>533</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>510</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -7946,7 +8219,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>534</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7954,22 +8227,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>536</v>
+        <v>559</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>538</v>
+        <v>561</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7977,45 +8250,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>542</v>
+        <v>565</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>545</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>547</v>
+        <v>570</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8023,22 +8296,22 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>552</v>
+        <v>575</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>553</v>
+        <v>576</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8046,22 +8319,22 @@
         <v>326</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8069,22 +8342,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8092,22 +8365,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8115,22 +8388,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8138,22 +8411,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8161,22 +8434,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>543</v>
+        <v>566</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8184,22 +8457,22 @@
         <v>177</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8207,22 +8480,22 @@
         <v>185</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8230,45 +8503,45 @@
         <v>181</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>599</v>
+        <v>622</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>602</v>
+        <v>625</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>604</v>
+        <v>627</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8276,45 +8549,45 @@
         <v>212</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>213</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>611</v>
+        <v>634</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>612</v>
+        <v>635</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>613</v>
+        <v>636</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>614</v>
+        <v>637</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>615</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="642">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
@@ -522,6 +522,15 @@
   </si>
   <si>
     <t xml:space="preserve">Spread of maintenance cost_amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANGED (Stage 12b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed on 2026-10-14 after the data profile showed repairs at 24.7% of rental billing. Damage-repair costs were scaled by 0.4 (Stage 12b). Original values: 2% / 8% / 25%. The new target of about 10% of rental billing is a judgement, not a sourced figure.</t>
   </si>
   <si>
     <t xml:space="preserve">R06</t>
@@ -1947,13 +1956,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="0%;\-0%"/>
     <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -2090,7 +2100,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2152,6 +2162,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2522,7 +2536,7 @@
       </c>
       <c r="B22" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Accept")</f>
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,7 +2545,7 @@
       </c>
       <c r="B23" s="6" t="n">
         <f aca="false">COUNTIF(Parameters!M5:M200,"Change")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3954,14 +3968,14 @@
       <c r="C36" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D36" s="13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>0.25</v>
+      <c r="D36" s="15" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>95</v>
@@ -3977,24 +3991,24 @@
         <v>165</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>47</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>149</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>1</v>
@@ -4016,27 +4030,27 @@
         <v>43</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M37" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>149</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>10</v>
@@ -4058,7 +4072,7 @@
         <v>43</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>45</v>
@@ -4072,13 +4086,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D39" s="14" t="n">
         <v>14</v>
@@ -4096,13 +4110,13 @@
         <v>42</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>45</v>
@@ -4116,13 +4130,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D40" s="14" t="n">
         <v>60</v>
@@ -4140,13 +4154,13 @@
         <v>42</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>45</v>
@@ -4160,13 +4174,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D41" s="14" t="n">
         <v>25</v>
@@ -4184,13 +4198,13 @@
         <v>42</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L41" s="8" t="s">
         <v>45</v>
@@ -4204,13 +4218,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>30</v>
@@ -4228,13 +4242,13 @@
         <v>42</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>45</v>
@@ -4248,13 +4262,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D43" s="14" t="n">
         <v>30</v>
@@ -4272,13 +4286,13 @@
         <v>42</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>45</v>
@@ -4292,13 +4306,13 @@
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D44" s="13" t="n">
         <v>0.5</v>
@@ -4316,13 +4330,13 @@
         <v>42</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J44" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>45</v>
@@ -4336,13 +4350,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>3</v>
@@ -4364,7 +4378,7 @@
         <v>43</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>45</v>
@@ -4378,13 +4392,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>0.1</v>
@@ -4406,7 +4420,7 @@
         <v>43</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>45</v>
@@ -4420,13 +4434,13 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D47" s="13" t="n">
         <v>0.1</v>
@@ -4448,7 +4462,7 @@
         <v>43</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L47" s="8" t="s">
         <v>45</v>
@@ -4462,13 +4476,13 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>1</v>
@@ -4490,7 +4504,7 @@
         <v>43</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>45</v>
@@ -4504,13 +4518,13 @@
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D49" s="13" t="n">
         <v>0.16</v>
@@ -4525,36 +4539,36 @@
         <v>95</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D50" s="12" t="n">
         <v>8</v>
@@ -4576,7 +4590,7 @@
         <v>43</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>45</v>
@@ -4590,13 +4604,13 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D51" s="12" t="n">
         <v>8</v>
@@ -4618,7 +4632,7 @@
         <v>43</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>45</v>
@@ -4632,13 +4646,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>222</v>
-      </c>
       <c r="C52" s="8" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D52" s="12" t="n">
         <v>4</v>
@@ -4660,7 +4674,7 @@
         <v>43</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>45</v>
@@ -4674,13 +4688,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D53" s="12" t="n">
         <v>4</v>
@@ -4702,7 +4716,7 @@
         <v>43</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>45</v>
@@ -4716,13 +4730,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D54" s="12" t="n">
         <v>5</v>
@@ -4744,7 +4758,7 @@
         <v>43</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>45</v>
@@ -4758,13 +4772,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D55" s="12" t="n">
         <v>3</v>
@@ -4786,7 +4800,7 @@
         <v>43</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>45</v>
@@ -4800,13 +4814,13 @@
     </row>
     <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="13" t="n">
@@ -4824,27 +4838,27 @@
         <v>43</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M56" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="13" t="n">
@@ -4862,27 +4876,27 @@
         <v>43</v>
       </c>
       <c r="K57" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N57" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="13" t="n">
@@ -4900,27 +4914,27 @@
         <v>43</v>
       </c>
       <c r="K58" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N58" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="L58" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M58" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N58" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="13" t="n">
@@ -4938,27 +4952,27 @@
         <v>43</v>
       </c>
       <c r="K59" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N59" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="13" t="n">
@@ -4976,27 +4990,27 @@
         <v>43</v>
       </c>
       <c r="K60" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N60" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="L60" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M60" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N60" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="13" t="n">
@@ -5014,27 +5028,27 @@
         <v>43</v>
       </c>
       <c r="K61" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N61" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="L61" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="13" t="n">
@@ -5052,27 +5066,27 @@
         <v>43</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="13" t="n">
@@ -5086,33 +5100,33 @@
         <v>42</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M63" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="13" t="n">
@@ -5126,33 +5140,33 @@
         <v>42</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L64" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M64" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="13" t="n">
@@ -5166,37 +5180,37 @@
         <v>42</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M65" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="9" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8" t="s">
@@ -5210,31 +5224,31 @@
         <v>43</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L66" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M66" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8" t="s">
@@ -5248,31 +5262,31 @@
         <v>43</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M67" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="9" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8" t="s">
@@ -5286,31 +5300,31 @@
         <v>43</v>
       </c>
       <c r="K68" s="8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L68" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M68" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="9" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="8" t="s">
@@ -5324,27 +5338,27 @@
         <v>43</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M69" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D70" s="11" t="n">
         <v>100</v>
@@ -5366,27 +5380,27 @@
         <v>43</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M70" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D71" s="13" t="n">
         <v>0.03</v>
@@ -5408,27 +5422,27 @@
         <v>43</v>
       </c>
       <c r="K71" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N71" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="L71" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N71" s="10" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D72" s="13" t="n">
         <v>0.02</v>
@@ -5450,31 +5464,31 @@
         <v>43</v>
       </c>
       <c r="K72" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8" t="s">
@@ -5488,31 +5502,31 @@
         <v>43</v>
       </c>
       <c r="K73" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M73" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8" t="s">
@@ -5526,31 +5540,31 @@
         <v>43</v>
       </c>
       <c r="K74" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L74" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F75" s="8"/>
       <c r="G75" s="8" t="s">
@@ -5564,31 +5578,31 @@
         <v>43</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M75" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F76" s="8"/>
       <c r="G76" s="8" t="s">
@@ -5602,27 +5616,27 @@
         <v>43</v>
       </c>
       <c r="K76" s="8" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L76" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M76" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N76" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D77" s="13" t="n">
         <v>0.1</v>
@@ -5644,27 +5658,27 @@
         <v>43</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M77" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D78" s="13" t="n">
         <v>0.6</v>
@@ -5686,27 +5700,27 @@
         <v>43</v>
       </c>
       <c r="K78" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="L78" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="M78" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N78" s="10" t="s">
         <v>317</v>
-      </c>
-      <c r="L78" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="M78" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N78" s="10" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D79" s="13" t="n">
         <v>0.2</v>
@@ -5728,27 +5742,27 @@
         <v>43</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M79" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D80" s="13" t="n">
         <v>-0.05</v>
@@ -5770,27 +5784,27 @@
         <v>43</v>
       </c>
       <c r="K80" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M80" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N80" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="13" t="n">
@@ -5804,33 +5818,33 @@
         <v>42</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J81" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K81" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M81" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="13" t="n">
@@ -5844,33 +5858,33 @@
         <v>42</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J82" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M82" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N82" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="13" t="n">
@@ -5890,27 +5904,27 @@
         <v>114</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M83" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="13" t="n">
@@ -5928,27 +5942,27 @@
         <v>43</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M84" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N84" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D85" s="8"/>
       <c r="E85" s="13" t="n">
@@ -5966,27 +5980,27 @@
         <v>43</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M85" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="8" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D86" s="12" t="n">
         <v>1500</v>
@@ -6008,27 +6022,27 @@
         <v>43</v>
       </c>
       <c r="K86" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M86" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N86" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D87" s="12" t="n">
         <v>2500</v>
@@ -6050,31 +6064,31 @@
         <v>43</v>
       </c>
       <c r="K87" s="8" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M87" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="8" t="s">
@@ -6090,31 +6104,31 @@
         <v>114</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L88" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M88" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="8" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="8" t="s">
@@ -6128,31 +6142,31 @@
         <v>43</v>
       </c>
       <c r="K89" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M89" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="8" t="s">
@@ -6166,31 +6180,31 @@
         <v>43</v>
       </c>
       <c r="K90" s="8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M90" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D91" s="8"/>
       <c r="E91" s="9" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F91" s="8"/>
       <c r="G91" s="8" t="s">
@@ -6204,31 +6218,31 @@
         <v>43</v>
       </c>
       <c r="K91" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M91" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="8" t="s">
@@ -6242,31 +6256,31 @@
         <v>43</v>
       </c>
       <c r="K92" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M92" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N92" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D93" s="8"/>
       <c r="E93" s="9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="8" t="s">
@@ -6282,27 +6296,27 @@
         <v>114</v>
       </c>
       <c r="K93" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M93" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D94" s="12" t="n">
         <v>450</v>
@@ -6324,27 +6338,27 @@
         <v>43</v>
       </c>
       <c r="K94" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L94" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M94" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N94" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D95" s="13" t="n">
         <v>0.3</v>
@@ -6366,27 +6380,27 @@
         <v>43</v>
       </c>
       <c r="K95" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N95" s="10" t="s">
         <v>376</v>
-      </c>
-      <c r="L95" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="M95" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N95" s="10" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D96" s="12" t="n">
         <v>20</v>
@@ -6408,27 +6422,27 @@
         <v>43</v>
       </c>
       <c r="K96" s="8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M96" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N96" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D97" s="13" t="n">
         <v>0</v>
@@ -6450,35 +6464,35 @@
         <v>43</v>
       </c>
       <c r="K97" s="8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M97" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="8" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D98" s="15" t="n">
+        <v>387</v>
+      </c>
+      <c r="D98" s="16" t="n">
         <v>1.05</v>
       </c>
-      <c r="E98" s="15" t="n">
+      <c r="E98" s="16" t="n">
         <v>1.1</v>
       </c>
-      <c r="F98" s="15" t="n">
+      <c r="F98" s="16" t="n">
         <v>1.2</v>
       </c>
       <c r="G98" s="8" t="s">
@@ -6492,31 +6506,31 @@
         <v>43</v>
       </c>
       <c r="K98" s="8" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M98" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N98" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D99" s="8"/>
       <c r="E99" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8" t="s">
@@ -6530,31 +6544,31 @@
         <v>43</v>
       </c>
       <c r="K99" s="8" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M99" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="8" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D100" s="8"/>
       <c r="E100" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="8" t="s">
@@ -6568,31 +6582,31 @@
         <v>43</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M100" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N100" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D101" s="8"/>
       <c r="E101" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F101" s="8"/>
       <c r="G101" s="8" t="s">
@@ -6606,31 +6620,31 @@
         <v>43</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M101" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D102" s="8"/>
       <c r="E102" s="9" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="8" t="s">
@@ -6644,27 +6658,27 @@
         <v>43</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M102" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N102" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="8" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D103" s="13" t="n">
         <v>0.02</v>
@@ -6686,27 +6700,27 @@
         <v>43</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M103" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="8" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D104" s="11" t="n">
         <v>1.5</v>
@@ -6728,27 +6742,27 @@
         <v>43</v>
       </c>
       <c r="K104" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="M104" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N104" s="10" t="s">
         <v>410</v>
-      </c>
-      <c r="L104" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="M104" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N104" s="10" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="8" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D105" s="11" t="n">
         <v>2</v>
@@ -6770,27 +6784,27 @@
         <v>43</v>
       </c>
       <c r="K105" s="8" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L105" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M105" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="8" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D106" s="13" t="n">
         <v>0</v>
@@ -6812,31 +6826,31 @@
         <v>43</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L106" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M106" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N106" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="8" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D107" s="8"/>
       <c r="E107" s="9" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="8" t="s">
@@ -6850,31 +6864,31 @@
         <v>43</v>
       </c>
       <c r="K107" s="8" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L107" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M107" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D108" s="8"/>
       <c r="E108" s="9" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="8" t="s">
@@ -6888,31 +6902,31 @@
         <v>43</v>
       </c>
       <c r="K108" s="8" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L108" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M108" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N108" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D109" s="8"/>
       <c r="E109" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="8" t="s">
@@ -6922,37 +6936,37 @@
         <v>42</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="K109" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L109" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M109" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="8" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D110" s="8"/>
       <c r="E110" s="9" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="8" t="s">
@@ -6968,31 +6982,31 @@
         <v>114</v>
       </c>
       <c r="K110" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L110" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M110" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N110" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D111" s="8"/>
       <c r="E111" s="9" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F111" s="8"/>
       <c r="G111" s="8" t="s">
@@ -7006,27 +7020,27 @@
         <v>43</v>
       </c>
       <c r="K111" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M111" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="8" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D112" s="13" t="n">
         <v>0.15</v>
@@ -7048,27 +7062,27 @@
         <v>43</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M112" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N112" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D113" s="13" t="n">
         <v>0.2</v>
@@ -7090,31 +7104,31 @@
         <v>43</v>
       </c>
       <c r="K113" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="M113" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N113" s="10" t="s">
         <v>446</v>
-      </c>
-      <c r="L113" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="M113" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N113" s="10" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D114" s="8"/>
       <c r="E114" s="9" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F114" s="8"/>
       <c r="G114" s="8" t="s">
@@ -7128,31 +7142,31 @@
         <v>43</v>
       </c>
       <c r="K114" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L114" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M114" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="8" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D115" s="8"/>
       <c r="E115" s="9" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F115" s="8"/>
       <c r="G115" s="8" t="s">
@@ -7168,27 +7182,27 @@
         <v>114</v>
       </c>
       <c r="K115" s="8" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L115" s="8" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M115" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="8" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D116" s="13" t="n">
         <v>0.3</v>
@@ -7206,37 +7220,37 @@
         <v>42</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K116" s="8" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L116" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M116" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N116" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B117" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="M116" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N116" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>456</v>
-      </c>
       <c r="C117" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D117" s="8"/>
       <c r="E117" s="9" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F117" s="8"/>
       <c r="G117" s="8" t="s">
@@ -7246,37 +7260,37 @@
         <v>42</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J117" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K117" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L117" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M117" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N117" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B118" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="M117" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N117" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>456</v>
-      </c>
       <c r="C118" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D118" s="8"/>
       <c r="E118" s="9" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F118" s="8"/>
       <c r="G118" s="8" t="s">
@@ -7286,37 +7300,37 @@
         <v>42</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J118" s="8" t="s">
         <v>97</v>
       </c>
       <c r="K118" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L118" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M118" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N118" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="B119" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="M118" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N118" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>456</v>
-      </c>
       <c r="C119" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D119" s="8"/>
       <c r="E119" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F119" s="8"/>
       <c r="G119" s="8" t="s">
@@ -7330,31 +7344,31 @@
         <v>43</v>
       </c>
       <c r="K119" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L119" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M119" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B120" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="M119" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N119" s="10" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>456</v>
-      </c>
       <c r="C120" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D120" s="8"/>
       <c r="E120" s="9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F120" s="8"/>
       <c r="G120" s="8" t="s">
@@ -7368,16 +7382,16 @@
         <v>43</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L120" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M120" s="10" t="s">
         <v>46</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -7442,26 +7456,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>30</v>
@@ -7475,10 +7489,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>6000</v>
@@ -7493,15 +7507,15 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -7516,15 +7530,15 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -7539,15 +7553,15 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -7562,15 +7576,15 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -7585,15 +7599,15 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -7608,15 +7622,15 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -7631,15 +7645,15 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -7654,15 +7668,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -7677,15 +7691,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -7700,15 +7714,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -7723,15 +7737,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -7746,15 +7760,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -7769,15 +7783,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -7792,7 +7806,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -7832,12 +7846,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7845,22 +7859,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -7868,26 +7882,26 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="D5" s="16" t="n">
+        <v>514</v>
+      </c>
+      <c r="D5" s="17" t="n">
         <f aca="false">Parameters!E51</f>
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -7895,26 +7909,26 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="D6" s="16" t="n">
+        <v>519</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <f aca="false">Parameters!E52</f>
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -7922,26 +7936,26 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="D7" s="16" t="n">
+        <v>523</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <f aca="false">Parameters!E53</f>
         <v>6</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -7949,26 +7963,26 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="D8" s="16" t="n">
+        <v>514</v>
+      </c>
+      <c r="D8" s="17" t="n">
         <f aca="false">Parameters!E54</f>
         <v>8</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -7976,26 +7990,26 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="D9" s="16" t="n">
+        <v>519</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <f aca="false">Parameters!E55</f>
         <v>5</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -8003,15 +8017,15 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="D10" s="17" t="n">
+        <v>534</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <f aca="false">Parameters!E26</f>
         <v>0.25</v>
       </c>
@@ -8019,10 +8033,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -8030,15 +8044,15 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="D11" s="17" t="n">
+        <v>539</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">Parameters!E28</f>
         <v>-0.05</v>
       </c>
@@ -8046,10 +8060,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -8057,26 +8071,26 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="D12" s="16" t="n">
+        <v>543</v>
+      </c>
+      <c r="D12" s="17" t="n">
         <f aca="false">Parameters!E45</f>
         <v>4</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -8084,26 +8098,26 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="D13" s="16" t="n">
+        <v>547</v>
+      </c>
+      <c r="D13" s="17" t="n">
         <f aca="false">Parameters!E38</f>
         <v>15</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -8111,15 +8125,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="D14" s="17" t="n">
+        <v>550</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <f aca="false">Parameters!E34</f>
         <v>0.07</v>
       </c>
@@ -8127,10 +8141,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -8138,26 +8152,26 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="D15" s="16" t="n">
+        <v>554</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <f aca="false">Parameters!E50</f>
         <v>10</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -8165,15 +8179,15 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="D16" s="18" t="n">
+        <v>558</v>
+      </c>
+      <c r="D16" s="19" t="n">
         <f aca="false">Parameters!E22</f>
         <v>15</v>
       </c>
@@ -8181,10 +8195,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -8219,7 +8233,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8227,22 +8241,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8250,45 +8264,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8296,45 +8310,45 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8342,22 +8356,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8365,22 +8379,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8388,22 +8402,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8411,22 +8425,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8434,160 +8448,160 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assumptions_register.xlsx
+++ b/docs/assumptions_register.xlsx
@@ -24,24 +24,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="641">
   <si>
     <t xml:space="preserve">Mwangaza AV: assumptions register (synthetic case study)</t>
   </si>
   <si>
-    <t xml:space="preserve">STATUS: all values ACCEPTED as proposed by the owner on 2026-10-10 (Option B: bulk accept, not reviewed row by row). Two rows still need work: P11 (VAT) must be verified, and R06 (seasonality) is unknown. You can still change any row later.</t>
+    <t xml:space="preserve">STATUS: all values are accepted as working assumptions (2026-10-10). Two rows still need work: P11 (VAT) must be verified, and R06 (seasonality) is unknown. Any row can be revisited.</t>
   </si>
   <si>
     <t xml:space="preserve">HOW TO USE</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue numbers are proposed values (inputs). Black text is explanation. Green numbers on Planted_problems are links to the Parameters sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow cells (Parameters, columns M and N) are for you. Pick Accept, Change or Reject, and write what you want in the note.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: Decision = Change. Note = 'Use 100 customers, not 150, because the company is small.'</t>
+    <t xml:space="preserve">Blue numbers are assumed values (inputs). Black text is explanation. Green numbers on Planted_problems are links to the Parameters sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns M and N of the Parameters sheet record the review decision (Accept, Change or Reject) and a note for each row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example: Decision = Change; Note = the reason for the change.</t>
   </si>
   <si>
     <t xml:space="preserve">SOURCE GRADES</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">READ THIS BEFORE USING ANY NUMBER</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Most sources are vendors or trade magazines, mostly from the US and UK. No Kenyan AV-specific data was found. I cannot verify these ranges for a Kenyan business.</t>
+    <t xml:space="preserve">1. Most sources are vendors or trade magazines, mostly from the US and UK. No Kenyan AV-specific data was found. These ranges could not be verified for a Kenyan business.</t>
   </si>
   <si>
     <t xml:space="preserve">2. 'Central' is a starting value we chose inside the range. It is NOT a verified average.</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Parameters for the synthetic data generator</t>
   </si>
   <si>
-    <t xml:space="preserve">All values are PROPOSED. Edit the yellow columns (M and N). Low, Central and High are a range, not a verified average.</t>
+    <t xml:space="preserve">Values are working assumptions. Columns M and N record the review decision and a note. Low, Central and High form a range, not a verified average.</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">Status</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner note</t>
+    <t xml:space="preserve">Decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
   </si>
   <si>
     <t xml:space="preserve">G01</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">Dates the generator fills with activity</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (bulk)</t>
+    <t xml:space="preserve">ACCEPTED</t>
   </si>
   <si>
     <t xml:space="preserve">Accept</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulk accepted as proposed by the owner (Option B), not reviewed row by row.</t>
+    <t xml:space="preserve">Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">G02</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">Nairobi and Mombasa (both Kenya, fictional)</t>
   </si>
   <si>
-    <t xml:space="preserve">Two offices in one country keeps one currency and avoids copying any real firm's footprint. Changed from my earlier Kenya/Tanzania suggestion.</t>
+    <t xml:space="preserve">Two offices in one country keep one currency and avoid copying any real firm's footprint.</t>
   </si>
   <si>
     <t xml:space="preserve">G06</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">UNKNOWN: proposed placeholder</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulk accepted as proposed by the owner (Option B), not reviewed row by row. Kenyan seasonality is still unknown.</t>
+    <t xml:space="preserve">Accepted as a working value. Kenyan seasonality is still unknown.</t>
   </si>
   <si>
     <t xml:space="preserve">R07</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">VERIFY BEFORE USE</t>
   </si>
   <si>
-    <t xml:space="preserve">Bulk accepted as proposed by the owner (Option B), not reviewed row by row. VAT rate must still be verified before use.</t>
+    <t xml:space="preserve">Accepted as a working value. VAT rate must still be verified before use.</t>
   </si>
   <si>
     <t xml:space="preserve">S01</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">Share of customers in this sector (generator uses running totals)</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 6; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 6. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">SM2</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">purchase_cost on asset. PLACEHOLDER: Kenyan prices not verified.</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 7; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 7. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">R09</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">Quotes with status expired and no decision date</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 8; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 8. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">OF1</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">Rows in sales_order. Includes orders that come from quotes and orders with no quote</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 9; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 9. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">V02</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">The assets marked idle in Stage 7. Must stay under 10%</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 10; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 10. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">R13</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">Sets how many rental quotes are won. Rental quotes in total = won quotes divided by the win rate C03</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 11; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 11. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">R12</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">Sets which customers are prompt payers, so that the share of invoices paid over 30 days after the invoice (P06) lands near 60%. Prompt payers are never the habitual late payers (P07)</t>
   </si>
   <si>
-    <t xml:space="preserve">ACCEPTED (added Stage 12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 12; covered by the owner's 'use the proposed numbers' choice. Say so if you want to change it.</t>
+    <t xml:space="preserve">ACCEPTED (Stage 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added at Stage 12. Accepted as a working value.</t>
   </si>
   <si>
     <t xml:space="preserve">G39</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">Price bands per category (KES, before VAT)</t>
   </si>
   <si>
-    <t xml:space="preserve">PLACEHOLDERS for realistic scale. Not Kenyan market prices; I cannot verify those. Product bands sit inside parameter M08, asset bands inside M09.</t>
+    <t xml:space="preserve">PLACEHOLDERS for realistic scale. Not Kenyan market prices; these could not be verified. Product bands sit inside parameter M08, asset bands inside M09.</t>
   </si>
   <si>
     <t xml:space="preserve">Item type</t>
@@ -1491,9 +1491,6 @@
   </si>
   <si>
     <t xml:space="preserve">Microphones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added at Stage 7; covered by the owner's 'use the proposed numbers' choice.</t>
   </si>
   <si>
     <t xml:space="preserve">Loudspeakers and amplifiers</t>
@@ -7507,7 +7504,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7515,7 +7512,7 @@
         <v>487</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>15000</v>
@@ -7530,7 +7527,7 @@
         <v>46</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7538,7 +7535,7 @@
         <v>487</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>40000</v>
@@ -7553,7 +7550,7 @@
         <v>46</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7561,7 +7558,7 @@
         <v>487</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>60000</v>
@@ -7576,7 +7573,7 @@
         <v>46</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7584,7 +7581,7 @@
         <v>487</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>50000</v>
@@ -7599,7 +7596,7 @@
         <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7607,7 +7604,7 @@
         <v>487</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>2000</v>
@@ -7622,7 +7619,7 @@
         <v>46</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7630,7 +7627,7 @@
         <v>487</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>10000</v>
@@ -7645,7 +7642,7 @@
         <v>46</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7653,7 +7650,7 @@
         <v>487</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>5000</v>
@@ -7668,15 +7665,15 @@
         <v>46</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>497</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>498</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>1500</v>
@@ -7691,15 +7688,15 @@
         <v>46</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>5000</v>
@@ -7714,15 +7711,15 @@
         <v>46</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4000</v>
@@ -7737,15 +7734,15 @@
         <v>46</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>3000</v>
@@ -7760,15 +7757,15 @@
         <v>46</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>15000</v>
@@ -7783,15 +7780,15 @@
         <v>46</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>6000</v>
@@ -7806,7 +7803,7 @@
         <v>46</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>489</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -7846,12 +7843,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7859,22 +7856,22 @@
         <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>510</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>511</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>34</v>
@@ -7882,13 +7879,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>513</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>514</v>
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">Parameters!E51</f>
@@ -7898,10 +7895,10 @@
         <v>224</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>515</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>516</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>45</v>
@@ -7909,13 +7906,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>519</v>
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">Parameters!E52</f>
@@ -7925,10 +7922,10 @@
         <v>228</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>45</v>
@@ -7936,13 +7933,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">Parameters!E53</f>
@@ -7952,10 +7949,10 @@
         <v>231</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>524</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>45</v>
@@ -7963,13 +7960,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>527</v>
-      </c>
       <c r="C8" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">Parameters!E54</f>
@@ -7979,10 +7976,10 @@
         <v>234</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>45</v>
@@ -7990,13 +7987,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>530</v>
-      </c>
       <c r="C9" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">Parameters!E55</f>
@@ -8006,10 +8003,10 @@
         <v>237</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>45</v>
@@ -8017,13 +8014,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>533</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>534</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">Parameters!E26</f>
@@ -8033,10 +8030,10 @@
         <v>130</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>535</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>536</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>45</v>
@@ -8044,13 +8041,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>538</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">Parameters!E28</f>
@@ -8060,10 +8057,10 @@
         <v>137</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>45</v>
@@ -8071,13 +8068,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>541</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">Parameters!E45</f>
@@ -8087,10 +8084,10 @@
         <v>200</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>45</v>
@@ -8098,13 +8095,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">Parameters!E38</f>
@@ -8114,10 +8111,10 @@
         <v>174</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>45</v>
@@ -8125,13 +8122,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">Parameters!E34</f>
@@ -8141,10 +8138,10 @@
         <v>156</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>45</v>
@@ -8152,13 +8149,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>554</v>
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">Parameters!E50</f>
@@ -8168,10 +8165,10 @@
         <v>220</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>45</v>
@@ -8179,13 +8176,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>557</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>558</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">Parameters!E22</f>
@@ -8195,10 +8192,10 @@
         <v>111</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>45</v>
@@ -8233,7 +8230,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8241,22 +8238,22 @@
         <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>565</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8264,45 +8261,45 @@
         <v>132</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>568</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>569</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F5" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>576</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8310,22 +8307,22 @@
         <v>128</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>579</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>580</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>581</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8333,22 +8330,22 @@
         <v>329</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>584</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>585</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>586</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8356,22 +8353,22 @@
         <v>101</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>589</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>590</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>591</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8379,22 +8376,22 @@
         <v>109</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>593</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>594</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F9" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>595</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8402,22 +8399,22 @@
         <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>598</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>599</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8425,22 +8422,22 @@
         <v>155</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
         <v>603</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>604</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>605</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8448,22 +8445,22 @@
         <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>608</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F12" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>609</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8471,22 +8468,22 @@
         <v>180</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>613</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F13" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>614</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8494,22 +8491,22 @@
         <v>188</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>618</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F14" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>619</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8517,45 +8514,45 @@
         <v>184</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>623</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>624</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>628</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>629</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8563,45 +8560,45 @@
         <v>215</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>633</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>634</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>216</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>635</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>638</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>639</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>641</v>
       </c>
     </row>
   </sheetData>
